--- a/backend/storage/imports/Master_SBM/18. SATUAN BIAYA TIKET PESAWAT PERJALANAN DINAS LUAR NEGERI PERGI PULANG (PP).xlsx
+++ b/backend/storage/imports/Master_SBM/18. SATUAN BIAYA TIKET PESAWAT PERJALANAN DINAS LUAR NEGERI PERGI PULANG (PP).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\imports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF69663-A152-49EF-B1C2-C1A3BA3FF26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C311B550-19A3-49CE-B489-975E81AAE0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{571A7D11-C42A-423F-BBD2-5953E26A535A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>(dalam  US$)</t>
   </si>
@@ -45,18 +45,6 @@
     <t>KOTA</t>
   </si>
   <si>
-    <t>BESARAN</t>
-  </si>
-  <si>
-    <t>EKSEKUTIF</t>
-  </si>
-  <si>
-    <t>BISNIS</t>
-  </si>
-  <si>
-    <t>EKONOMI</t>
-  </si>
-  <si>
     <t>AMERIKA  UTARA</t>
   </si>
   <si>
@@ -1498,6 +1486,15 @@
   </si>
   <si>
     <t>SATUAN BIAYA TIKET PESAWAT PERJALANAN DINAS LUAR NEGERI PERGI PULANG (PP)</t>
+  </si>
+  <si>
+    <t>BESARAN EKSEKUTIF</t>
+  </si>
+  <si>
+    <t>BESARAN BISNIS</t>
+  </si>
+  <si>
+    <t>BESARAN EKONOMI</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1550,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1587,56 +1584,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1652,7 +1599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1669,64 +1616,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2043,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38A25C9-EFDE-4447-AA4A-1B655DD7176C}">
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37.5546875" customWidth="1"/>
@@ -2057,7 +1992,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2079,577 +2014,585 @@
       <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>-1</v>
+      </c>
+      <c r="B4" s="7">
+        <v>-2</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>-4</v>
+      </c>
+      <c r="E4" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="6" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>-1</v>
-      </c>
-      <c r="B5" s="7">
-        <v>-2</v>
-      </c>
-      <c r="C5" s="7">
-        <v>-3</v>
-      </c>
-      <c r="D5" s="7">
-        <v>-4</v>
-      </c>
-      <c r="E5" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="C6" s="12">
+        <v>12733</v>
+      </c>
+      <c r="D6" s="12">
+        <v>6891</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3662</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="12">
-        <v>12733</v>
+        <v>12635</v>
       </c>
       <c r="D7" s="12">
-        <v>6891</v>
+        <v>6487</v>
       </c>
       <c r="E7" s="12">
-        <v>3662</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="12">
-        <v>12635</v>
+        <v>11411</v>
       </c>
       <c r="D8" s="12">
-        <v>6487</v>
+        <v>5925</v>
       </c>
       <c r="E8" s="12">
-        <v>3591</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" s="12">
-        <v>11411</v>
+        <v>15101</v>
       </c>
       <c r="D9" s="12">
-        <v>5925</v>
+        <v>6179</v>
       </c>
       <c r="E9" s="12">
-        <v>3242</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="12">
-        <v>15101</v>
+        <v>12266</v>
       </c>
       <c r="D10" s="12">
-        <v>6179</v>
+        <v>6924</v>
       </c>
       <c r="E10" s="12">
-        <v>3839</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" s="12">
-        <v>12266</v>
+        <v>13438</v>
       </c>
       <c r="D11" s="12">
-        <v>6924</v>
+        <v>7138</v>
       </c>
       <c r="E11" s="12">
-        <v>4083</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="12">
-        <v>13438</v>
+        <v>11750</v>
       </c>
       <c r="D12" s="12">
-        <v>7138</v>
+        <v>8564</v>
       </c>
       <c r="E12" s="12">
-        <v>2987</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="12">
-        <v>11750</v>
+        <v>10902</v>
       </c>
       <c r="D13" s="12">
-        <v>8564</v>
+        <v>7458</v>
       </c>
       <c r="E13" s="12">
-        <v>3201</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="12">
-        <v>10902</v>
+        <v>15150</v>
       </c>
       <c r="D14" s="12">
-        <v>7458</v>
+        <v>8652</v>
       </c>
       <c r="E14" s="12">
-        <v>3277</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>9</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="12">
-        <v>15150</v>
-      </c>
-      <c r="D15" s="12">
-        <v>8652</v>
-      </c>
-      <c r="E15" s="12">
-        <v>3930</v>
-      </c>
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+      <c r="A16" s="16">
+        <v>10</v>
+      </c>
       <c r="B16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="C16" s="17">
+        <v>18399</v>
+      </c>
+      <c r="D16" s="17">
+        <v>9426</v>
+      </c>
+      <c r="E16" s="17">
+        <v>7713</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C17" s="17">
-        <v>18399</v>
+        <v>16393</v>
       </c>
       <c r="D17" s="17">
-        <v>9426</v>
+        <v>11518</v>
       </c>
       <c r="E17" s="17">
-        <v>7713</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C18" s="17">
-        <v>16393</v>
+        <v>23000</v>
       </c>
       <c r="D18" s="17">
-        <v>11518</v>
+        <v>15300</v>
       </c>
       <c r="E18" s="17">
-        <v>5970</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C19" s="17">
-        <v>23000</v>
+        <v>23128</v>
       </c>
       <c r="D19" s="17">
-        <v>15300</v>
+        <v>13837</v>
       </c>
       <c r="E19" s="17">
-        <v>10400</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C20" s="17">
-        <v>23128</v>
+        <v>15018</v>
       </c>
       <c r="D20" s="17">
-        <v>13837</v>
+        <v>9494</v>
       </c>
       <c r="E20" s="17">
-        <v>6825</v>
+        <v>7353</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" s="17">
-        <v>15018</v>
+        <v>21874</v>
       </c>
       <c r="D21" s="17">
-        <v>9494</v>
+        <v>15539</v>
       </c>
       <c r="E21" s="17">
-        <v>7353</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C22" s="17">
-        <v>21874</v>
+        <v>17325</v>
       </c>
       <c r="D22" s="17">
-        <v>15539</v>
+        <v>16269</v>
       </c>
       <c r="E22" s="17">
-        <v>8900</v>
+        <v>12127</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C23" s="17">
-        <v>17325</v>
+        <v>8263</v>
       </c>
       <c r="D23" s="17">
-        <v>16269</v>
+        <v>8263</v>
       </c>
       <c r="E23" s="17">
-        <v>12127</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>17</v>
-      </c>
+      <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="17">
-        <v>8263</v>
-      </c>
-      <c r="D24" s="17">
-        <v>8263</v>
-      </c>
-      <c r="E24" s="17">
-        <v>5038</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="16">
+        <v>18</v>
+      </c>
       <c r="B25" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+        <v>23</v>
+      </c>
+      <c r="C25" s="17">
+        <v>11822</v>
+      </c>
+      <c r="D25" s="17">
+        <v>7831</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3966</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C26" s="17">
-        <v>11822</v>
+        <v>14702</v>
       </c>
       <c r="D26" s="17">
-        <v>7831</v>
+        <v>11223</v>
       </c>
       <c r="E26" s="17">
-        <v>3966</v>
+        <v>7335</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C27" s="17">
-        <v>14702</v>
+        <v>15532</v>
       </c>
       <c r="D27" s="17">
-        <v>11223</v>
+        <v>9306</v>
       </c>
       <c r="E27" s="17">
-        <v>7335</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
-        <v>20</v>
-      </c>
+      <c r="A28" s="13"/>
       <c r="B28" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="17">
-        <v>15532</v>
-      </c>
-      <c r="D28" s="17">
-        <v>9306</v>
-      </c>
-      <c r="E28" s="17">
-        <v>6195</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
+      <c r="A29" s="16">
+        <v>21</v>
+      </c>
       <c r="B29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="C29" s="17">
+        <v>10520</v>
+      </c>
+      <c r="D29" s="17">
+        <v>4177</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3357</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C30" s="17">
-        <v>10520</v>
+        <v>10713</v>
       </c>
       <c r="D30" s="17">
-        <v>4177</v>
+        <v>5994</v>
       </c>
       <c r="E30" s="17">
-        <v>3357</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C31" s="17">
-        <v>10713</v>
+        <v>10850</v>
       </c>
       <c r="D31" s="17">
-        <v>5994</v>
+        <v>5074</v>
       </c>
       <c r="E31" s="17">
-        <v>3870</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
-        <v>23</v>
+      <c r="A32" s="18">
+        <v>24</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C32" s="17">
-        <v>10850</v>
+        <v>10724</v>
       </c>
       <c r="D32" s="17">
-        <v>5074</v>
+        <v>6085</v>
       </c>
       <c r="E32" s="17">
-        <v>3541</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="18">
-        <v>24</v>
+      <c r="A33" s="16">
+        <v>25</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C33" s="17">
-        <v>10724</v>
+        <v>10277</v>
       </c>
       <c r="D33" s="17">
-        <v>6085</v>
+        <v>6126</v>
       </c>
       <c r="E33" s="17">
-        <v>3331</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" s="17">
-        <v>10277</v>
+        <v>11478</v>
       </c>
       <c r="D34" s="17">
-        <v>6126</v>
+        <v>6778</v>
       </c>
       <c r="E34" s="17">
-        <v>3959</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35" s="17">
-        <v>11478</v>
+        <v>10945</v>
       </c>
       <c r="D35" s="17">
-        <v>6778</v>
+        <v>5023</v>
       </c>
       <c r="E35" s="17">
-        <v>4355</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" s="17">
-        <v>10945</v>
+        <v>9938</v>
       </c>
       <c r="D36" s="17">
-        <v>5023</v>
+        <v>7639</v>
       </c>
       <c r="E36" s="17">
-        <v>3753</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" s="17">
-        <v>9938</v>
+        <v>8166</v>
       </c>
       <c r="D37" s="17">
-        <v>7639</v>
+        <v>5370</v>
       </c>
       <c r="E37" s="17">
-        <v>4108</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C38" s="17">
-        <v>8166</v>
+        <v>8216</v>
       </c>
       <c r="D38" s="17">
-        <v>5370</v>
+        <v>5898</v>
       </c>
       <c r="E38" s="17">
-        <v>4333</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" s="17">
         <v>8216</v>
@@ -2663,454 +2606,454 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C40" s="17">
-        <v>8216</v>
+        <v>7660</v>
       </c>
       <c r="D40" s="17">
-        <v>5898</v>
+        <v>4037</v>
       </c>
       <c r="E40" s="17">
-        <v>3331</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
-        <v>32</v>
-      </c>
+      <c r="A41" s="13"/>
       <c r="B41" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="17">
-        <v>7660</v>
-      </c>
-      <c r="D41" s="17">
-        <v>4037</v>
-      </c>
-      <c r="E41" s="17">
-        <v>1065</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
+      <c r="A42" s="16">
+        <v>33</v>
+      </c>
       <c r="B42" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="C42" s="17">
+        <v>9696</v>
+      </c>
+      <c r="D42" s="17">
+        <v>4920</v>
+      </c>
+      <c r="E42" s="17">
+        <v>3730</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C43" s="17">
-        <v>9696</v>
+        <v>10023</v>
       </c>
       <c r="D43" s="17">
-        <v>4920</v>
+        <v>5931</v>
       </c>
       <c r="E43" s="17">
-        <v>3730</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C44" s="17">
-        <v>10023</v>
+        <v>9917</v>
       </c>
       <c r="D44" s="17">
-        <v>5931</v>
+        <v>5506</v>
       </c>
       <c r="E44" s="17">
-        <v>3681</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C45" s="17">
-        <v>9917</v>
+        <v>11410</v>
       </c>
       <c r="D45" s="17">
-        <v>5506</v>
+        <v>7293</v>
       </c>
       <c r="E45" s="17">
-        <v>3433</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C46" s="17">
-        <v>11410</v>
+        <v>9856</v>
       </c>
       <c r="D46" s="17">
-        <v>7293</v>
+        <v>4773</v>
       </c>
       <c r="E46" s="17">
-        <v>4153</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="16">
-        <v>37</v>
-      </c>
+      <c r="A47" s="13"/>
       <c r="B47" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="17">
-        <v>9856</v>
-      </c>
-      <c r="D47" s="17">
-        <v>4773</v>
-      </c>
-      <c r="E47" s="17">
-        <v>4049</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
+      <c r="A48" s="16">
+        <v>38</v>
+      </c>
       <c r="B48" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
+        <v>46</v>
+      </c>
+      <c r="C48" s="17">
+        <v>11778</v>
+      </c>
+      <c r="D48" s="17">
+        <v>7129</v>
+      </c>
+      <c r="E48" s="17">
+        <v>6033</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C49" s="17">
-        <v>11778</v>
+        <v>16974</v>
       </c>
       <c r="D49" s="17">
-        <v>7129</v>
+        <v>10177</v>
       </c>
       <c r="E49" s="17">
-        <v>6033</v>
+        <v>5182</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="16">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C50" s="17">
-        <v>16974</v>
+        <v>14911</v>
       </c>
       <c r="D50" s="17">
-        <v>10177</v>
+        <v>9256</v>
       </c>
       <c r="E50" s="17">
-        <v>5182</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="16">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C51" s="17">
-        <v>14911</v>
+        <v>9309</v>
       </c>
       <c r="D51" s="17">
-        <v>9256</v>
+        <v>4746</v>
       </c>
       <c r="E51" s="17">
-        <v>8041</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C52" s="17">
-        <v>9309</v>
+        <v>10393</v>
       </c>
       <c r="D52" s="17">
-        <v>4746</v>
+        <v>4767</v>
       </c>
       <c r="E52" s="17">
-        <v>3383</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C53" s="17">
-        <v>10393</v>
+        <v>10000</v>
       </c>
       <c r="D53" s="17">
-        <v>4767</v>
+        <v>6000</v>
       </c>
       <c r="E53" s="17">
-        <v>3631</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="16">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C54" s="17">
-        <v>10000</v>
+        <v>10318</v>
       </c>
       <c r="D54" s="17">
-        <v>6000</v>
+        <v>6404</v>
       </c>
       <c r="E54" s="17">
-        <v>4500</v>
+        <v>5564</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="16">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C55" s="17">
-        <v>10318</v>
+        <v>10000</v>
       </c>
       <c r="D55" s="17">
-        <v>6404</v>
+        <v>6000</v>
       </c>
       <c r="E55" s="17">
-        <v>5564</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="16">
-        <v>45</v>
-      </c>
+      <c r="A56" s="13"/>
       <c r="B56" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="17">
-        <v>10000</v>
-      </c>
-      <c r="D56" s="17">
-        <v>6000</v>
-      </c>
-      <c r="E56" s="17">
-        <v>4500</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
+      <c r="A57" s="16">
+        <v>46</v>
+      </c>
       <c r="B57" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="C57" s="17">
+        <v>7125</v>
+      </c>
+      <c r="D57" s="17">
+        <v>4423</v>
+      </c>
+      <c r="E57" s="17">
+        <v>3842</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="16">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C58" s="17">
-        <v>7125</v>
+        <v>8839</v>
       </c>
       <c r="D58" s="17">
-        <v>4423</v>
+        <v>4982</v>
       </c>
       <c r="E58" s="17">
-        <v>3842</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="16">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C59" s="17">
-        <v>8839</v>
+        <v>10860</v>
       </c>
       <c r="D59" s="17">
-        <v>4982</v>
+        <v>6029</v>
       </c>
       <c r="E59" s="17">
-        <v>4113</v>
+        <v>5193</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="16">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C60" s="17">
-        <v>10860</v>
+        <v>9537</v>
       </c>
       <c r="D60" s="17">
-        <v>6029</v>
+        <v>7206</v>
       </c>
       <c r="E60" s="17">
-        <v>5193</v>
+        <v>5143</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="16">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C61" s="17">
-        <v>9537</v>
+        <v>19318</v>
       </c>
       <c r="D61" s="17">
-        <v>7206</v>
+        <v>11848</v>
       </c>
       <c r="E61" s="17">
-        <v>5143</v>
+        <v>6748</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C62" s="17">
-        <v>19318</v>
+        <v>7473</v>
       </c>
       <c r="D62" s="17">
-        <v>11848</v>
+        <v>6346</v>
       </c>
       <c r="E62" s="17">
-        <v>6748</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="16">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C63" s="17">
-        <v>7473</v>
+        <v>10777</v>
       </c>
       <c r="D63" s="17">
-        <v>6346</v>
+        <v>5052</v>
       </c>
       <c r="E63" s="17">
-        <v>3612</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C64" s="17">
-        <v>10777</v>
+        <v>8839</v>
       </c>
       <c r="D64" s="17">
-        <v>5052</v>
+        <v>5979</v>
       </c>
       <c r="E64" s="17">
-        <v>3447</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="16">
-        <v>53</v>
-      </c>
+      <c r="A65" s="13"/>
       <c r="B65" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" s="17">
-        <v>8839</v>
-      </c>
-      <c r="D65" s="17">
-        <v>5979</v>
-      </c>
-      <c r="E65" s="17">
-        <v>2187</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
+      <c r="A66" s="16">
+        <v>54</v>
+      </c>
       <c r="B66" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
+        <v>64</v>
+      </c>
+      <c r="C66" s="17">
+        <v>12900</v>
+      </c>
+      <c r="D66" s="17">
+        <v>9848</v>
+      </c>
+      <c r="E66" s="17">
+        <v>8555</v>
+      </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="16">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C67" s="17">
-        <v>12900</v>
+        <v>10281</v>
       </c>
       <c r="D67" s="17">
-        <v>9848</v>
+        <v>7848</v>
       </c>
       <c r="E67" s="17">
-        <v>8555</v>
+        <v>6818</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="16">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C68" s="17">
         <v>10281</v>
@@ -3123,359 +3066,359 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="16">
-        <v>56</v>
-      </c>
+      <c r="A69" s="13"/>
       <c r="B69" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="17">
-        <v>10281</v>
-      </c>
-      <c r="D69" s="17">
-        <v>7848</v>
-      </c>
-      <c r="E69" s="17">
-        <v>6818</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
+      <c r="A70" s="16">
+        <v>57</v>
+      </c>
       <c r="B70" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
+        <v>68</v>
+      </c>
+      <c r="C70" s="17">
+        <v>7700</v>
+      </c>
+      <c r="D70" s="17">
+        <v>5808</v>
+      </c>
+      <c r="E70" s="17">
+        <v>5552</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="16">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C71" s="17">
-        <v>7700</v>
+        <v>8732</v>
       </c>
       <c r="D71" s="17">
-        <v>5808</v>
+        <v>7966</v>
       </c>
       <c r="E71" s="17">
-        <v>5552</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="16">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C72" s="17">
-        <v>8732</v>
+        <v>11779</v>
       </c>
       <c r="D72" s="17">
-        <v>7966</v>
+        <v>9000</v>
       </c>
       <c r="E72" s="17">
-        <v>6081</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="16">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C73" s="17">
-        <v>11779</v>
+        <v>8947</v>
       </c>
       <c r="D73" s="17">
-        <v>9000</v>
+        <v>6599</v>
       </c>
       <c r="E73" s="17">
-        <v>8282</v>
+        <v>5733</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C74" s="17">
-        <v>8947</v>
+        <v>11118</v>
       </c>
       <c r="D74" s="17">
-        <v>6599</v>
+        <v>10600</v>
       </c>
       <c r="E74" s="17">
-        <v>5733</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="16">
-        <v>61</v>
-      </c>
+      <c r="A75" s="13"/>
       <c r="B75" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="17">
-        <v>11118</v>
-      </c>
-      <c r="D75" s="17">
-        <v>10600</v>
-      </c>
-      <c r="E75" s="17">
-        <v>5747</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
+      <c r="A76" s="16">
+        <v>62</v>
+      </c>
       <c r="B76" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
+        <v>74</v>
+      </c>
+      <c r="C76" s="17">
+        <v>18241</v>
+      </c>
+      <c r="D76" s="17">
+        <v>11774</v>
+      </c>
+      <c r="E76" s="17">
+        <v>7510</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="16">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C77" s="17">
-        <v>18241</v>
+        <v>17182</v>
       </c>
       <c r="D77" s="17">
-        <v>11774</v>
+        <v>9703</v>
       </c>
       <c r="E77" s="17">
-        <v>7510</v>
+        <v>8429</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="16">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B78" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C78" s="17">
+        <v>12943</v>
+      </c>
+      <c r="D78" s="17">
+        <v>9802</v>
+      </c>
+      <c r="E78" s="17">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18">
+        <v>65</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" s="17">
+        <v>11255</v>
+      </c>
+      <c r="D79" s="17">
+        <v>8524</v>
+      </c>
+      <c r="E79" s="17">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="16">
+        <v>66</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="17">
+        <v>12943</v>
+      </c>
+      <c r="D80" s="17">
+        <v>9802</v>
+      </c>
+      <c r="E80" s="17">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="13"/>
+      <c r="B81" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="17">
-        <v>17182</v>
-      </c>
-      <c r="D78" s="17">
-        <v>9703</v>
-      </c>
-      <c r="E78" s="17">
-        <v>8429</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="16">
-        <v>64</v>
-      </c>
-      <c r="B79" s="14" t="s">
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="16">
+        <v>67</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C79" s="17">
-        <v>12943</v>
-      </c>
-      <c r="D79" s="17">
-        <v>9802</v>
-      </c>
-      <c r="E79" s="17">
-        <v>7216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="18">
-        <v>65</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C80" s="17">
-        <v>11255</v>
-      </c>
-      <c r="D80" s="17">
-        <v>8524</v>
-      </c>
-      <c r="E80" s="17">
-        <v>6275</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="16">
-        <v>66</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C81" s="17">
-        <v>12943</v>
-      </c>
-      <c r="D81" s="17">
-        <v>9802</v>
-      </c>
-      <c r="E81" s="17">
-        <v>7216</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
+      <c r="C82" s="17">
+        <v>9536</v>
+      </c>
+      <c r="D82" s="17">
+        <v>6593</v>
+      </c>
+      <c r="E82" s="17">
+        <v>5710</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="16">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C83" s="17">
-        <v>9536</v>
+        <v>8683</v>
       </c>
       <c r="D83" s="17">
-        <v>6593</v>
+        <v>7122</v>
       </c>
       <c r="E83" s="17">
-        <v>5710</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="16">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C84" s="17">
-        <v>8683</v>
+        <v>5904</v>
       </c>
       <c r="D84" s="17">
-        <v>7122</v>
+        <v>4507</v>
       </c>
       <c r="E84" s="17">
-        <v>4483</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="16">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C85" s="17">
-        <v>5904</v>
+        <v>8910</v>
       </c>
       <c r="D85" s="17">
-        <v>4507</v>
+        <v>7721</v>
       </c>
       <c r="E85" s="17">
-        <v>3915</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="16">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C86" s="17">
-        <v>8910</v>
+        <v>6551</v>
       </c>
       <c r="D86" s="17">
-        <v>7721</v>
+        <v>5706</v>
       </c>
       <c r="E86" s="17">
-        <v>5665</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="16">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C87" s="17">
-        <v>6551</v>
+        <v>9419</v>
       </c>
       <c r="D87" s="17">
-        <v>5706</v>
+        <v>5018</v>
       </c>
       <c r="E87" s="17">
-        <v>4975</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="16">
-        <v>72</v>
-      </c>
+      <c r="A88" s="13"/>
       <c r="B88" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="17">
-        <v>9419</v>
-      </c>
-      <c r="D88" s="17">
-        <v>5018</v>
-      </c>
-      <c r="E88" s="17">
-        <v>3619</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="13"/>
+      <c r="A89" s="16">
+        <v>73</v>
+      </c>
       <c r="B89" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
+        <v>87</v>
+      </c>
+      <c r="C89" s="17">
+        <v>6573</v>
+      </c>
+      <c r="D89" s="17">
+        <v>6154</v>
+      </c>
+      <c r="E89" s="17">
+        <v>4827</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="16">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C90" s="17">
-        <v>6573</v>
+        <v>5433</v>
       </c>
       <c r="D90" s="17">
-        <v>6154</v>
+        <v>4148</v>
       </c>
       <c r="E90" s="17">
-        <v>4827</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="16">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C91" s="17">
-        <v>5433</v>
+        <v>7561</v>
       </c>
       <c r="D91" s="17">
-        <v>4148</v>
+        <v>6431</v>
       </c>
       <c r="E91" s="17">
         <v>3545</v>
@@ -3483,402 +3426,402 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="16">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C92" s="17">
-        <v>7561</v>
+        <v>6771</v>
       </c>
       <c r="D92" s="17">
-        <v>6431</v>
+        <v>4273</v>
       </c>
       <c r="E92" s="17">
-        <v>3545</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="16">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C93" s="17">
-        <v>6771</v>
+        <v>7703</v>
       </c>
       <c r="D93" s="17">
-        <v>4273</v>
+        <v>4490</v>
       </c>
       <c r="E93" s="17">
-        <v>3110</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="16">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C94" s="17">
-        <v>7703</v>
+        <v>5216</v>
       </c>
       <c r="D94" s="17">
-        <v>4490</v>
+        <v>3639</v>
       </c>
       <c r="E94" s="17">
-        <v>3730</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="16">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C95" s="17">
-        <v>5216</v>
+        <v>8684</v>
       </c>
       <c r="D95" s="17">
-        <v>3639</v>
+        <v>5390</v>
       </c>
       <c r="E95" s="17">
-        <v>2745</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="16">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C96" s="17">
-        <v>8684</v>
+        <v>9449</v>
       </c>
       <c r="D96" s="17">
-        <v>5390</v>
+        <v>6643</v>
       </c>
       <c r="E96" s="17">
-        <v>3325</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="16">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C97" s="17">
-        <v>9449</v>
+        <v>5283</v>
       </c>
       <c r="D97" s="17">
-        <v>6643</v>
+        <v>4976</v>
       </c>
       <c r="E97" s="17">
-        <v>3581</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="16">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B98" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C98" s="17">
-        <v>5283</v>
+        <v>8205</v>
       </c>
       <c r="D98" s="17">
-        <v>4976</v>
+        <v>5878</v>
       </c>
       <c r="E98" s="17">
-        <v>2727</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="16">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C99" s="17">
-        <v>8205</v>
+        <v>6446</v>
       </c>
       <c r="D99" s="17">
-        <v>5878</v>
+        <v>3785</v>
       </c>
       <c r="E99" s="17">
-        <v>3679</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="16">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B100" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C100" s="17">
-        <v>6446</v>
+        <v>6469</v>
       </c>
       <c r="D100" s="17">
-        <v>3785</v>
+        <v>5156</v>
       </c>
       <c r="E100" s="17">
-        <v>3321</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="16">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C101" s="17">
-        <v>6469</v>
+        <v>5359</v>
       </c>
       <c r="D101" s="17">
-        <v>5156</v>
+        <v>3510</v>
       </c>
       <c r="E101" s="17">
-        <v>3727</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="16">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C102" s="17">
-        <v>5359</v>
+        <v>11061</v>
       </c>
       <c r="D102" s="17">
-        <v>3510</v>
+        <v>4435</v>
       </c>
       <c r="E102" s="17">
-        <v>3000</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="16">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C103" s="17">
-        <v>11061</v>
+        <v>4207</v>
       </c>
       <c r="D103" s="17">
-        <v>4435</v>
+        <v>4207</v>
       </c>
       <c r="E103" s="17">
-        <v>2467</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="16">
-        <v>87</v>
-      </c>
+      <c r="A104" s="13"/>
       <c r="B104" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" s="17">
-        <v>4207</v>
-      </c>
-      <c r="D104" s="17">
-        <v>4207</v>
-      </c>
-      <c r="E104" s="17">
-        <v>1920</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C104" s="15"/>
+      <c r="D104" s="15"/>
+      <c r="E104" s="15"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="13"/>
+      <c r="A105" s="16">
+        <v>88</v>
+      </c>
       <c r="B105" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" s="15"/>
-      <c r="D105" s="15"/>
-      <c r="E105" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="C105" s="17">
+        <v>13617</v>
+      </c>
+      <c r="D105" s="17">
+        <v>8453</v>
+      </c>
+      <c r="E105" s="17">
+        <v>7343</v>
+      </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="16">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C106" s="17">
-        <v>13617</v>
+        <v>13661</v>
       </c>
       <c r="D106" s="17">
-        <v>8453</v>
+        <v>12089</v>
       </c>
       <c r="E106" s="17">
-        <v>7343</v>
+        <v>8962</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="16">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C107" s="17">
-        <v>13661</v>
+        <v>13234</v>
       </c>
       <c r="D107" s="17">
-        <v>12089</v>
+        <v>8556</v>
       </c>
       <c r="E107" s="17">
-        <v>8962</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="16">
-        <v>90</v>
-      </c>
+      <c r="A108" s="13"/>
       <c r="B108" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C108" s="17">
-        <v>13234</v>
-      </c>
-      <c r="D108" s="17">
-        <v>8556</v>
-      </c>
-      <c r="E108" s="17">
-        <v>2281</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="13"/>
+      <c r="A109" s="16">
+        <v>91</v>
+      </c>
       <c r="B109" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
-      <c r="E109" s="15"/>
+        <v>107</v>
+      </c>
+      <c r="C109" s="17">
+        <v>2595</v>
+      </c>
+      <c r="D109" s="17">
+        <v>2140</v>
+      </c>
+      <c r="E109" s="17">
+        <v>1623</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="16">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C110" s="17">
-        <v>2595</v>
+        <v>3028</v>
       </c>
       <c r="D110" s="17">
-        <v>2140</v>
+        <v>2633</v>
       </c>
       <c r="E110" s="17">
-        <v>1623</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="16">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C111" s="17">
-        <v>3028</v>
+        <v>3204</v>
       </c>
       <c r="D111" s="17">
-        <v>2633</v>
+        <v>2686</v>
       </c>
       <c r="E111" s="17">
-        <v>1257</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="16">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C112" s="17">
-        <v>3204</v>
+        <v>3734</v>
       </c>
       <c r="D112" s="17">
-        <v>2686</v>
+        <v>2675</v>
       </c>
       <c r="E112" s="17">
-        <v>1864</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="16">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C113" s="17">
-        <v>3734</v>
+        <v>4040</v>
       </c>
       <c r="D113" s="17">
-        <v>2675</v>
+        <v>2220</v>
       </c>
       <c r="E113" s="17">
-        <v>1835</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="16">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C114" s="17">
-        <v>4040</v>
+        <v>3233</v>
       </c>
       <c r="D114" s="17">
-        <v>2220</v>
+        <v>2966</v>
       </c>
       <c r="E114" s="17">
-        <v>1660</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="16">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C115" s="17">
-        <v>3233</v>
+        <v>3122</v>
       </c>
       <c r="D115" s="17">
-        <v>2966</v>
+        <v>2749</v>
       </c>
       <c r="E115" s="17">
-        <v>1737</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="16">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C116" s="17">
         <v>3122</v>
@@ -3891,667 +3834,645 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="16">
-        <v>98</v>
-      </c>
+      <c r="A117" s="13"/>
       <c r="B117" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C117" s="17">
-        <v>3122</v>
-      </c>
-      <c r="D117" s="17">
-        <v>2749</v>
-      </c>
-      <c r="E117" s="17">
-        <v>1304</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="13"/>
+      <c r="A118" s="16">
+        <v>99</v>
+      </c>
       <c r="B118" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C118" s="15"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
+        <v>116</v>
+      </c>
+      <c r="C118" s="17">
+        <v>6307</v>
+      </c>
+      <c r="D118" s="17">
+        <v>3905</v>
+      </c>
+      <c r="E118" s="17">
+        <v>3208</v>
+      </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="16">
-        <v>99</v>
+      <c r="A119" s="19">
+        <v>100</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C119" s="17">
-        <v>6307</v>
+        <v>5800</v>
       </c>
       <c r="D119" s="17">
-        <v>3905</v>
+        <v>4600</v>
       </c>
       <c r="E119" s="17">
-        <v>3208</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="19">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C120" s="17">
-        <v>5800</v>
+        <v>3119</v>
       </c>
       <c r="D120" s="17">
-        <v>4600</v>
+        <v>2562</v>
       </c>
       <c r="E120" s="17">
-        <v>3200</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="19">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C121" s="17">
-        <v>3119</v>
+        <v>3063</v>
       </c>
       <c r="D121" s="17">
-        <v>2562</v>
+        <v>2417</v>
       </c>
       <c r="E121" s="17">
-        <v>1628</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="19">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C122" s="17">
-        <v>3063</v>
+        <v>5482</v>
       </c>
       <c r="D122" s="17">
-        <v>2417</v>
+        <v>3333</v>
       </c>
       <c r="E122" s="17">
-        <v>1092</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="19">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C123" s="17">
-        <v>5482</v>
+        <v>4226</v>
       </c>
       <c r="D123" s="17">
-        <v>3333</v>
+        <v>3633</v>
       </c>
       <c r="E123" s="17">
-        <v>2501</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="19">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B124" s="14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C124" s="17">
-        <v>4226</v>
+        <v>3500</v>
       </c>
       <c r="D124" s="17">
-        <v>3633</v>
+        <v>2500</v>
       </c>
       <c r="E124" s="17">
-        <v>2321</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="19">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C125" s="17">
-        <v>3500</v>
+        <v>3063</v>
       </c>
       <c r="D125" s="17">
-        <v>2500</v>
+        <v>2417</v>
       </c>
       <c r="E125" s="17">
-        <v>1500</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="19">
-        <v>106</v>
-      </c>
+      <c r="A126" s="13"/>
       <c r="B126" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C126" s="17">
-        <v>3063</v>
-      </c>
-      <c r="D126" s="17">
-        <v>2417</v>
-      </c>
-      <c r="E126" s="17">
-        <v>1092</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="13"/>
+      <c r="A127" s="19">
+        <v>107</v>
+      </c>
       <c r="B127" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
+        <v>125</v>
+      </c>
+      <c r="C127" s="17">
+        <v>1628</v>
+      </c>
+      <c r="D127" s="17">
+        <v>1147</v>
+      </c>
+      <c r="E127" s="20">
+        <v>919</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="19">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C128" s="17">
-        <v>1628</v>
+        <v>2344</v>
       </c>
       <c r="D128" s="17">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="E128" s="20">
-        <v>919</v>
+        <v>823</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="19">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B129" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C129" s="17">
-        <v>2344</v>
+        <v>2757</v>
       </c>
       <c r="D129" s="17">
-        <v>1155</v>
-      </c>
-      <c r="E129" s="20">
-        <v>823</v>
+        <v>2558</v>
+      </c>
+      <c r="E129" s="17">
+        <v>1641</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="19">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B130" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C130" s="17">
-        <v>2757</v>
-      </c>
-      <c r="D130" s="17">
-        <v>2558</v>
-      </c>
-      <c r="E130" s="17">
-        <v>1641</v>
+        <v>128</v>
+      </c>
+      <c r="C130" s="20">
+        <v>747</v>
+      </c>
+      <c r="D130" s="20">
+        <v>491</v>
+      </c>
+      <c r="E130" s="20">
+        <v>350</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="19">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B131" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C131" s="20">
-        <v>747</v>
-      </c>
-      <c r="D131" s="20">
-        <v>491</v>
-      </c>
-      <c r="E131" s="20">
-        <v>350</v>
+        <v>129</v>
+      </c>
+      <c r="C131" s="17">
+        <v>1833</v>
+      </c>
+      <c r="D131" s="17">
+        <v>1833</v>
+      </c>
+      <c r="E131" s="17">
+        <v>1656</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="19">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B132" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C132" s="17">
-        <v>1833</v>
+        <v>1677</v>
       </c>
       <c r="D132" s="17">
-        <v>1833</v>
+        <v>1503</v>
       </c>
       <c r="E132" s="17">
-        <v>1656</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="19">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C133" s="17">
-        <v>1677</v>
-      </c>
-      <c r="D133" s="17">
-        <v>1503</v>
-      </c>
-      <c r="E133" s="17">
-        <v>1235</v>
+        <v>1195</v>
+      </c>
+      <c r="D133" s="20">
+        <v>911</v>
+      </c>
+      <c r="E133" s="20">
+        <v>525</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="19">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C134" s="17">
-        <v>1195</v>
-      </c>
-      <c r="D134" s="20">
-        <v>911</v>
+        <v>1894</v>
+      </c>
+      <c r="D134" s="17">
+        <v>1427</v>
       </c>
       <c r="E134" s="20">
-        <v>525</v>
+        <v>694</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="19">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C135" s="17">
-        <v>1894</v>
-      </c>
-      <c r="D135" s="17">
-        <v>1427</v>
+        <v>1158</v>
+      </c>
+      <c r="D135" s="20">
+        <v>659</v>
       </c>
       <c r="E135" s="20">
-        <v>694</v>
+        <v>585</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="19">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C136" s="17">
-        <v>1158</v>
-      </c>
-      <c r="D136" s="20">
-        <v>659</v>
+        <v>2659</v>
+      </c>
+      <c r="D136" s="17">
+        <v>1900</v>
       </c>
       <c r="E136" s="20">
-        <v>585</v>
+        <v>364</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="19">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B137" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C137" s="17">
-        <v>2659</v>
+        <v>2453</v>
       </c>
       <c r="D137" s="17">
-        <v>1900</v>
-      </c>
-      <c r="E137" s="20">
-        <v>364</v>
+        <v>1614</v>
+      </c>
+      <c r="E137" s="17">
+        <v>1150</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="19">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B138" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C138" s="17">
-        <v>2453</v>
-      </c>
-      <c r="D138" s="17">
-        <v>1614</v>
-      </c>
-      <c r="E138" s="17">
-        <v>1150</v>
+        <v>136</v>
+      </c>
+      <c r="C138" s="20">
+        <v>918</v>
+      </c>
+      <c r="D138" s="20">
+        <v>766</v>
+      </c>
+      <c r="E138" s="20">
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="19">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B139" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C139" s="20">
-        <v>918</v>
-      </c>
-      <c r="D139" s="20">
-        <v>766</v>
-      </c>
-      <c r="E139" s="20">
-        <v>545</v>
+        <v>137</v>
+      </c>
+      <c r="C139" s="17">
+        <v>2202</v>
+      </c>
+      <c r="D139" s="17">
+        <v>1981</v>
+      </c>
+      <c r="E139" s="17">
+        <v>1627</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="19">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C140" s="17">
-        <v>2202</v>
-      </c>
-      <c r="D140" s="17">
-        <v>1981</v>
-      </c>
-      <c r="E140" s="17">
-        <v>1627</v>
+        <v>138</v>
+      </c>
+      <c r="C140" s="20">
+        <v>991</v>
+      </c>
+      <c r="D140" s="20">
+        <v>673</v>
+      </c>
+      <c r="E140" s="20">
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="19">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B141" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C141" s="20">
-        <v>991</v>
-      </c>
-      <c r="D141" s="20">
-        <v>673</v>
-      </c>
-      <c r="E141" s="20">
-        <v>403</v>
+        <v>139</v>
+      </c>
+      <c r="C141" s="17">
+        <v>2274</v>
+      </c>
+      <c r="D141" s="17">
+        <v>2025</v>
+      </c>
+      <c r="E141" s="17">
+        <v>1420</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="19">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C142" s="17">
-        <v>2274</v>
+        <v>1468</v>
       </c>
       <c r="D142" s="17">
-        <v>2025</v>
+        <v>1212</v>
       </c>
       <c r="E142" s="17">
-        <v>1420</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="19">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C143" s="17">
-        <v>1468</v>
+        <v>1894</v>
       </c>
       <c r="D143" s="17">
-        <v>1212</v>
-      </c>
-      <c r="E143" s="17">
-        <v>1053</v>
+        <v>1427</v>
+      </c>
+      <c r="E143" s="20">
+        <v>694</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="19">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C144" s="17">
-        <v>1894</v>
+        <v>2344</v>
       </c>
       <c r="D144" s="17">
-        <v>1427</v>
+        <v>1155</v>
       </c>
       <c r="E144" s="20">
-        <v>694</v>
+        <v>823</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="19">
-        <v>124</v>
-      </c>
+      <c r="A145" s="13"/>
       <c r="B145" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C145" s="17">
-        <v>2344</v>
-      </c>
-      <c r="D145" s="17">
-        <v>1155</v>
-      </c>
-      <c r="E145" s="20">
-        <v>823</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C145" s="15"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="15"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="13"/>
+      <c r="A146" s="16">
+        <v>125</v>
+      </c>
       <c r="B146" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C146" s="15"/>
-      <c r="D146" s="15"/>
-      <c r="E146" s="15"/>
+        <v>144</v>
+      </c>
+      <c r="C146" s="17">
+        <v>6304</v>
+      </c>
+      <c r="D146" s="17">
+        <v>6304</v>
+      </c>
+      <c r="E146" s="17">
+        <v>2500</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="16">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B147" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C147" s="17">
-        <v>6304</v>
+        <v>6689</v>
       </c>
       <c r="D147" s="17">
-        <v>6304</v>
+        <v>4900</v>
       </c>
       <c r="E147" s="17">
-        <v>2500</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="16">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B148" s="14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C148" s="17">
-        <v>6689</v>
+        <v>4886</v>
       </c>
       <c r="D148" s="17">
-        <v>4900</v>
+        <v>3814</v>
       </c>
       <c r="E148" s="17">
-        <v>3964</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="16">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B149" s="14" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C149" s="17">
-        <v>4886</v>
+        <v>6940</v>
       </c>
       <c r="D149" s="17">
-        <v>3814</v>
+        <v>5917</v>
       </c>
       <c r="E149" s="17">
-        <v>2858</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="16">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C150" s="17">
-        <v>6940</v>
+        <v>5771</v>
       </c>
       <c r="D150" s="17">
-        <v>5917</v>
+        <v>1801</v>
       </c>
       <c r="E150" s="17">
-        <v>1916</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="16">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C151" s="17">
-        <v>5771</v>
+        <v>17090</v>
       </c>
       <c r="D151" s="17">
-        <v>1801</v>
+        <v>13835</v>
       </c>
       <c r="E151" s="17">
-        <v>1525</v>
+        <v>8252</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="16">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C152" s="17">
-        <v>17090</v>
+        <v>12668</v>
       </c>
       <c r="D152" s="17">
-        <v>13835</v>
+        <v>4461</v>
       </c>
       <c r="E152" s="17">
-        <v>8252</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="16">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B153" s="14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C153" s="17">
-        <v>12668</v>
+        <v>4629</v>
       </c>
       <c r="D153" s="17">
-        <v>4461</v>
+        <v>4237</v>
       </c>
       <c r="E153" s="17">
-        <v>2669</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="16">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B154" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C154" s="17">
-        <v>4629</v>
+        <v>3318</v>
       </c>
       <c r="D154" s="17">
-        <v>4237</v>
+        <v>2740</v>
       </c>
       <c r="E154" s="17">
-        <v>2557</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="16">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B155" s="14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C155" s="17">
-        <v>3318</v>
+        <v>11750</v>
       </c>
       <c r="D155" s="17">
-        <v>2740</v>
+        <v>9830</v>
       </c>
       <c r="E155" s="17">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="16">
-        <v>134</v>
-      </c>
-      <c r="B156" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="C156" s="17">
-        <v>11750</v>
-      </c>
-      <c r="D156" s="17">
-        <v>9830</v>
-      </c>
-      <c r="E156" s="17">
         <v>4120</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:E3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>